--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336C1EF9-D673-4EB1-84FF-729EB089E59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538F736B-E035-42A1-B334-CA02040DC1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -429,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -446,19 +446,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -470,8 +461,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -764,28 +758,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="10" t="s">
         <v>73</v>
       </c>
     </row>
@@ -793,24 +787,24 @@
       <c r="A3" s="4">
         <v>46139</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46140</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -820,14 +814,14 @@
         <v>13</v>
       </c>
       <c r="E4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46141</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -836,7 +830,7 @@
       <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="11">
         <v>2.5</v>
       </c>
     </row>
@@ -844,7 +838,7 @@
       <c r="A6" s="4">
         <v>46142</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -858,28 +852,28 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="10" t="s">
         <v>73</v>
       </c>
     </row>
@@ -896,7 +890,7 @@
       <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="11">
         <v>2.5</v>
       </c>
     </row>
@@ -907,7 +901,7 @@
       <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -938,7 +932,7 @@
       <c r="A12" s="4">
         <v>46146</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -955,7 +949,7 @@
       <c r="A13" s="4">
         <v>46147</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -972,7 +966,7 @@
       <c r="A14" s="4">
         <v>46148</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -989,7 +983,7 @@
       <c r="A15" s="4">
         <v>46149</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1057,7 +1051,7 @@
       <c r="A19" s="4">
         <v>46153</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1074,7 +1068,7 @@
       <c r="A20" s="4">
         <v>46154</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1091,7 +1085,7 @@
       <c r="A21" s="4">
         <v>46155</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1108,7 +1102,7 @@
       <c r="A22" s="4">
         <v>46156</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1176,7 +1170,7 @@
       <c r="A26" s="4">
         <v>46160</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -1193,7 +1187,7 @@
       <c r="A27" s="4">
         <v>46161</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1210,7 +1204,7 @@
       <c r="A28" s="4">
         <v>46162</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="5" t="s">
@@ -1227,7 +1221,7 @@
       <c r="A29" s="4">
         <v>46163</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="5" t="s">
@@ -1295,7 +1289,7 @@
       <c r="A33" s="4">
         <v>46167</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="5" t="s">
@@ -1312,7 +1306,7 @@
       <c r="A34" s="4">
         <v>46168</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="5" t="s">
@@ -1329,7 +1323,7 @@
       <c r="A35" s="4">
         <v>46169</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C35" s="5" t="s">
@@ -1346,7 +1340,7 @@
       <c r="A36" s="4">
         <v>46170</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="5" t="s">
@@ -1411,28 +1405,28 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
     </row>
     <row r="41" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="10" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1440,7 +1434,7 @@
       <c r="A42" s="4">
         <v>46174</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -1457,7 +1451,7 @@
       <c r="A43" s="4">
         <v>46175</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="5" t="s">
@@ -1474,7 +1468,7 @@
       <c r="A44" s="4">
         <v>46176</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="5" t="s">
@@ -1491,7 +1485,7 @@
       <c r="A45" s="4">
         <v>46177</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C45" s="5" t="s">
@@ -1559,7 +1553,7 @@
       <c r="A49" s="4">
         <v>46181</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C49" s="5" t="s">
@@ -1576,7 +1570,7 @@
       <c r="A50" s="4">
         <v>46182</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C50" s="5" t="s">
@@ -1593,7 +1587,7 @@
       <c r="A51" s="4">
         <v>46183</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="5" t="s">
@@ -1610,7 +1604,7 @@
       <c r="A52" s="4">
         <v>46184</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -1678,7 +1672,7 @@
       <c r="A56" s="4">
         <v>46188</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C56" s="5" t="s">
@@ -1695,7 +1689,7 @@
       <c r="A57" s="4">
         <v>46189</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="5" t="s">
@@ -1712,7 +1706,7 @@
       <c r="A58" s="4">
         <v>46190</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C58" s="5" t="s">
@@ -1729,7 +1723,7 @@
       <c r="A59" s="4">
         <v>46191</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C59" s="5" t="s">
@@ -1797,7 +1791,7 @@
       <c r="A63" s="4">
         <v>46195</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C63" s="5" t="s">
@@ -1814,7 +1808,7 @@
       <c r="A64" s="4">
         <v>46196</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="5" t="s">
@@ -1831,7 +1825,7 @@
       <c r="A65" s="4">
         <v>46197</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C65" s="5" t="s">
@@ -1848,7 +1842,7 @@
       <c r="A66" s="4">
         <v>46198</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C66" s="5" t="s">
@@ -1916,7 +1910,7 @@
       <c r="A70" s="4">
         <v>46202</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C70" s="5" t="s">
@@ -1933,7 +1927,7 @@
       <c r="A71" s="4">
         <v>46203</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C71" s="5" t="s">
@@ -1947,28 +1941,28 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
     </row>
     <row r="73" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="13" t="s">
+      <c r="E73" s="10" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1976,7 +1970,7 @@
       <c r="A74" s="4">
         <v>46204</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C74" s="5" t="s">
@@ -1993,7 +1987,7 @@
       <c r="A75" s="4">
         <v>46205</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C75" s="5" t="s">
@@ -2061,7 +2055,7 @@
       <c r="A79" s="4">
         <v>46209</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C79" s="5" t="s">
@@ -2078,7 +2072,7 @@
       <c r="A80" s="4">
         <v>46210</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C80" s="5" t="s">
@@ -2095,7 +2089,7 @@
       <c r="A81" s="4">
         <v>46211</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C81" s="5" t="s">
@@ -2112,7 +2106,7 @@
       <c r="A82" s="4">
         <v>46212</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C82" s="5" t="s">
@@ -2180,7 +2174,7 @@
       <c r="A86" s="4">
         <v>46216</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C86" s="5" t="s">
@@ -2197,7 +2191,7 @@
       <c r="A87" s="4">
         <v>46217</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C87" s="5" t="s">
@@ -2214,7 +2208,7 @@
       <c r="A88" s="4">
         <v>46218</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C88" s="5" t="s">
@@ -2228,10 +2222,10 @@
       </c>
     </row>
     <row r="89" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="10"/>
+      <c r="B89" s="7"/>
     </row>
     <row r="90" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="7"/>
+      <c r="B90" s="6"/>
     </row>
     <row r="91" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="92" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538F736B-E035-42A1-B334-CA02040DC1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2826652C-FE29-4579-884D-7AD0BEC2B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -382,7 +382,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -398,6 +398,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -465,6 +471,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -793,7 +802,7 @@
       <c r="C3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="5">
@@ -810,7 +819,7 @@
       <c r="C4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="5">

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2826652C-FE29-4579-884D-7AD0BEC2B962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BEF82D-F124-4694-9C76-081FC0ADADC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -435,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -458,9 +458,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -470,10 +467,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -767,28 +770,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>73</v>
       </c>
     </row>
@@ -799,10 +802,10 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="5">
@@ -816,10 +819,10 @@
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="5">
@@ -839,7 +842,7 @@
       <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>2.5</v>
       </c>
     </row>
@@ -861,28 +864,28 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>73</v>
       </c>
     </row>
@@ -899,7 +902,7 @@
       <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>2.5</v>
       </c>
     </row>
@@ -1414,28 +1417,28 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
     </row>
     <row r="41" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="9" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1950,28 +1953,28 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
     </row>
     <row r="73" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D73" s="9" t="s">
+      <c r="D73" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="9" t="s">
         <v>73</v>
       </c>
     </row>

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BEF82D-F124-4694-9C76-081FC0ADADC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77E73C2-F422-41BE-8F8D-5C3DDAF9EF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5220" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -435,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -474,9 +474,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -797,7 +794,7 @@
     </row>
     <row r="3" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>17</v>
@@ -814,12 +811,12 @@
     </row>
     <row r="4" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>46140</v>
+        <v>46147</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="11" t="s">
@@ -831,7 +828,7 @@
     </row>
     <row r="5" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>19</v>
@@ -848,7 +845,7 @@
     </row>
     <row r="6" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
@@ -891,7 +888,7 @@
     </row>
     <row r="9" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>21</v>
@@ -908,7 +905,7 @@
     </row>
     <row r="10" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>22</v>
@@ -925,7 +922,7 @@
     </row>
     <row r="11" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>46145</v>
+        <v>46152</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>23</v>
@@ -942,7 +939,7 @@
     </row>
     <row r="12" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>17</v>
@@ -959,7 +956,7 @@
     </row>
     <row r="13" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>18</v>
@@ -976,7 +973,7 @@
     </row>
     <row r="14" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>19</v>
@@ -993,7 +990,7 @@
     </row>
     <row r="15" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -1010,7 +1007,7 @@
     </row>
     <row r="16" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>21</v>
@@ -1027,7 +1024,7 @@
     </row>
     <row r="17" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>22</v>
@@ -1044,7 +1041,7 @@
     </row>
     <row r="18" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>23</v>
@@ -1061,7 +1058,7 @@
     </row>
     <row r="19" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>17</v>
@@ -1078,7 +1075,7 @@
     </row>
     <row r="20" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>18</v>
@@ -1095,7 +1092,7 @@
     </row>
     <row r="21" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>19</v>
@@ -1112,7 +1109,7 @@
     </row>
     <row r="22" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
@@ -1129,7 +1126,7 @@
     </row>
     <row r="23" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>21</v>
@@ -1146,7 +1143,7 @@
     </row>
     <row r="24" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>22</v>
@@ -1163,7 +1160,7 @@
     </row>
     <row r="25" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>23</v>
@@ -1180,7 +1177,7 @@
     </row>
     <row r="26" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>17</v>
@@ -1197,7 +1194,7 @@
     </row>
     <row r="27" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>18</v>
@@ -1214,7 +1211,7 @@
     </row>
     <row r="28" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>19</v>
@@ -1231,7 +1228,7 @@
     </row>
     <row r="29" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>20</v>
@@ -1248,7 +1245,7 @@
     </row>
     <row r="30" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>21</v>
@@ -1265,7 +1262,7 @@
     </row>
     <row r="31" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>46165</v>
+        <v>46172</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>22</v>
@@ -1282,7 +1279,7 @@
     </row>
     <row r="32" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>23</v>
@@ -1299,7 +1296,7 @@
     </row>
     <row r="33" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>17</v>
@@ -1316,7 +1313,7 @@
     </row>
     <row r="34" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>46168</v>
+        <v>46175</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>18</v>
@@ -1333,7 +1330,7 @@
     </row>
     <row r="35" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>46169</v>
+        <v>46176</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>19</v>
@@ -1350,7 +1347,7 @@
     </row>
     <row r="36" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>46170</v>
+        <v>46177</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>20</v>
@@ -1367,7 +1364,7 @@
     </row>
     <row r="37" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>21</v>
@@ -1384,7 +1381,7 @@
     </row>
     <row r="38" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>46172</v>
+        <v>46179</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>22</v>
@@ -1401,7 +1398,7 @@
     </row>
     <row r="39" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>46173</v>
+        <v>46180</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>23</v>
@@ -1444,7 +1441,7 @@
     </row>
     <row r="42" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>17</v>
@@ -1461,7 +1458,7 @@
     </row>
     <row r="43" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>18</v>
@@ -1478,7 +1475,7 @@
     </row>
     <row r="44" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>19</v>
@@ -1495,7 +1492,7 @@
     </row>
     <row r="45" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>20</v>
@@ -1512,7 +1509,7 @@
     </row>
     <row r="46" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>21</v>
@@ -1529,7 +1526,7 @@
     </row>
     <row r="47" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>22</v>
@@ -1546,7 +1543,7 @@
     </row>
     <row r="48" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>23</v>
@@ -1563,7 +1560,7 @@
     </row>
     <row r="49" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>17</v>
@@ -1580,7 +1577,7 @@
     </row>
     <row r="50" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>18</v>
@@ -1597,7 +1594,7 @@
     </row>
     <row r="51" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>46183</v>
+        <v>46190</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>19</v>
@@ -1614,7 +1611,7 @@
     </row>
     <row r="52" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>46184</v>
+        <v>46191</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>20</v>
@@ -1631,7 +1628,7 @@
     </row>
     <row r="53" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>21</v>
@@ -1648,7 +1645,7 @@
     </row>
     <row r="54" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>22</v>
@@ -1665,7 +1662,7 @@
     </row>
     <row r="55" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>23</v>
@@ -1682,7 +1679,7 @@
     </row>
     <row r="56" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>17</v>
@@ -1699,7 +1696,7 @@
     </row>
     <row r="57" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>18</v>
@@ -1716,7 +1713,7 @@
     </row>
     <row r="58" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>19</v>
@@ -1733,7 +1730,7 @@
     </row>
     <row r="59" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>20</v>
@@ -1750,7 +1747,7 @@
     </row>
     <row r="60" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>21</v>
@@ -1767,7 +1764,7 @@
     </row>
     <row r="61" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>22</v>
@@ -1784,7 +1781,7 @@
     </row>
     <row r="62" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>23</v>
@@ -1801,7 +1798,7 @@
     </row>
     <row r="63" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>17</v>
@@ -1818,7 +1815,7 @@
     </row>
     <row r="64" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>18</v>
@@ -1835,7 +1832,7 @@
     </row>
     <row r="65" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>19</v>
@@ -1852,7 +1849,7 @@
     </row>
     <row r="66" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>20</v>
@@ -1869,7 +1866,7 @@
     </row>
     <row r="67" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>21</v>
@@ -1886,7 +1883,7 @@
     </row>
     <row r="68" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>22</v>
@@ -1903,7 +1900,7 @@
     </row>
     <row r="69" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>46201</v>
+        <v>46208</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>23</v>
@@ -1920,7 +1917,7 @@
     </row>
     <row r="70" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>17</v>
@@ -1937,7 +1934,7 @@
     </row>
     <row r="71" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>18</v>
@@ -1980,7 +1977,7 @@
     </row>
     <row r="74" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>19</v>
@@ -1997,7 +1994,7 @@
     </row>
     <row r="75" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>20</v>
@@ -2014,7 +2011,7 @@
     </row>
     <row r="76" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>21</v>
@@ -2031,7 +2028,7 @@
     </row>
     <row r="77" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>22</v>
@@ -2048,7 +2045,7 @@
     </row>
     <row r="78" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>23</v>
@@ -2065,7 +2062,7 @@
     </row>
     <row r="79" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>17</v>
@@ -2082,7 +2079,7 @@
     </row>
     <row r="80" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>18</v>
@@ -2099,7 +2096,7 @@
     </row>
     <row r="81" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>19</v>
@@ -2116,7 +2113,7 @@
     </row>
     <row r="82" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>46212</v>
+        <v>46219</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>20</v>
@@ -2133,7 +2130,7 @@
     </row>
     <row r="83" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>21</v>
@@ -2150,7 +2147,7 @@
     </row>
     <row r="84" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>22</v>
@@ -2167,7 +2164,7 @@
     </row>
     <row r="85" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>23</v>
@@ -2184,7 +2181,7 @@
     </row>
     <row r="86" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>17</v>
@@ -2201,7 +2198,7 @@
     </row>
     <row r="87" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>18</v>
@@ -2218,7 +2215,7 @@
     </row>
     <row r="88" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
-        <v>46218</v>
+        <v>46225</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>19</v>

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77E73C2-F422-41BE-8F8D-5C3DDAF9EF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565C8239-3FA0-4CDD-90F2-DF750D3F27F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5220" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="80">
   <si>
     <t>课程进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -337,6 +337,9 @@
   <si>
     <t>6h</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
   </si>
 </sst>
 </file>
@@ -1651,7 +1654,7 @@
         <v>22</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>64</v>

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565C8239-3FA0-4CDD-90F2-DF750D3F27F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1F1BE0-A6A9-488C-A975-4D715224D3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -759,17 +759,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="48.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="37.88671875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>11</v>
       </c>
@@ -778,7 +780,7 @@
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
     </row>
-    <row r="2" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -795,7 +797,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46146</v>
       </c>
@@ -812,7 +814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46147</v>
       </c>
@@ -829,41 +831,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46148</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="10">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46149</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="5">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
@@ -872,7 +874,7 @@
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
     </row>
-    <row r="8" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
@@ -889,41 +891,41 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46150</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="10">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46151</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="5">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46152</v>
       </c>
@@ -940,7 +942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46153</v>
       </c>
@@ -957,7 +959,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46154</v>
       </c>
@@ -974,7 +976,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46155</v>
       </c>
@@ -991,7 +993,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46156</v>
       </c>
@@ -1008,7 +1010,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46157</v>
       </c>

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1F1BE0-A6A9-488C-A975-4D715224D3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB5189F-229F-4A0B-97C4-4D820B07C6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -475,6 +475,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -759,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -771,16 +774,16 @@
     <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -797,7 +800,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46146</v>
       </c>
@@ -814,7 +817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46147</v>
       </c>
@@ -831,50 +834,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46148</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="10">
         <v>2.5</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46149</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="5">
         <v>2.5</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-    </row>
-    <row r="8" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
@@ -891,41 +894,41 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46150</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="10">
         <v>2.5</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46151</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="C10" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="5">
         <v>2.5</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46152</v>
       </c>
@@ -942,7 +945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46153</v>
       </c>
@@ -959,7 +962,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46154</v>
       </c>
@@ -976,7 +979,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46155</v>
       </c>
@@ -993,7 +996,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46156</v>
       </c>
@@ -1010,7 +1013,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46157</v>
       </c>
@@ -1419,13 +1422,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
     </row>
     <row r="41" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
@@ -1955,13 +1958,13 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
     </row>
     <row r="73" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB5189F-229F-4A0B-97C4-4D820B07C6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDFE655-CC8B-43F0-92BB-3B3244FEB650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="82">
   <si>
     <t>课程进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -340,6 +340,14 @@
   </si>
   <si>
     <t>无</t>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中值定理中微分方程反解C法（P9）未看</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -411,7 +419,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -434,11 +442,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -464,12 +485,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -480,6 +495,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -762,28 +792,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="48.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="29" style="17" customWidth="1"/>
     <col min="7" max="7" width="37.88671875" style="1" customWidth="1"/>
     <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:6" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -796,45 +826,48 @@
       <c r="D2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="13" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46146</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46147</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46148</v>
       </c>
@@ -844,40 +877,40 @@
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46149</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="14">
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:6" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
@@ -890,11 +923,11 @@
       <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46150</v>
       </c>
@@ -907,11 +940,11 @@
       <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46151</v>
       </c>
@@ -924,11 +957,11 @@
       <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="14">
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46152</v>
       </c>
@@ -941,11 +974,11 @@
       <c r="D11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46153</v>
       </c>
@@ -958,11 +991,11 @@
       <c r="D12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="14">
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46154</v>
       </c>
@@ -975,11 +1008,11 @@
       <c r="D13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46155</v>
       </c>
@@ -992,28 +1025,31 @@
       <c r="D14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46156</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46157</v>
       </c>
@@ -1026,9 +1062,10 @@
       <c r="D16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="E16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
@@ -1043,7 +1080,7 @@
       <c r="D17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1060,7 +1097,7 @@
       <c r="D18" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1077,7 +1114,7 @@
       <c r="D19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1094,7 +1131,7 @@
       <c r="D20" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1111,7 +1148,7 @@
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1128,7 +1165,7 @@
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1145,7 +1182,7 @@
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1162,7 +1199,7 @@
       <c r="D24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1179,7 +1216,7 @@
       <c r="D25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1196,7 +1233,7 @@
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1213,7 +1250,7 @@
       <c r="D27" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1230,7 +1267,7 @@
       <c r="D28" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1247,7 +1284,7 @@
       <c r="D29" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1264,7 +1301,7 @@
       <c r="D30" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1281,7 +1318,7 @@
       <c r="D31" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1298,7 +1335,7 @@
       <c r="D32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1315,7 +1352,7 @@
       <c r="D33" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1332,7 +1369,7 @@
       <c r="D34" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1349,7 +1386,7 @@
       <c r="D35" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1366,7 +1403,7 @@
       <c r="D36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1383,7 +1420,7 @@
       <c r="D37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1400,7 +1437,7 @@
       <c r="D38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1417,18 +1454,18 @@
       <c r="D39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
     </row>
     <row r="41" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
@@ -1443,7 +1480,7 @@
       <c r="D41" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="13" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1460,7 +1497,7 @@
       <c r="D42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1477,7 +1514,7 @@
       <c r="D43" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1494,7 +1531,7 @@
       <c r="D44" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1511,7 +1548,7 @@
       <c r="D45" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1528,7 +1565,7 @@
       <c r="D46" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1545,7 +1582,7 @@
       <c r="D47" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1562,7 +1599,7 @@
       <c r="D48" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1579,7 +1616,7 @@
       <c r="D49" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1596,7 +1633,7 @@
       <c r="D50" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1613,7 +1650,7 @@
       <c r="D51" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1630,7 +1667,7 @@
       <c r="D52" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1647,7 +1684,7 @@
       <c r="D53" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1664,7 +1701,7 @@
       <c r="D54" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1681,7 +1718,7 @@
       <c r="D55" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1698,7 +1735,7 @@
       <c r="D56" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1715,7 +1752,7 @@
       <c r="D57" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1732,7 +1769,7 @@
       <c r="D58" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1749,7 +1786,7 @@
       <c r="D59" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1766,7 +1803,7 @@
       <c r="D60" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1783,7 +1820,7 @@
       <c r="D61" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1800,7 +1837,7 @@
       <c r="D62" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1817,7 +1854,7 @@
       <c r="D63" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1834,7 +1871,7 @@
       <c r="D64" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1851,7 +1888,7 @@
       <c r="D65" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1868,7 +1905,7 @@
       <c r="D66" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1885,7 +1922,7 @@
       <c r="D67" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1902,7 +1939,7 @@
       <c r="D68" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1919,7 +1956,7 @@
       <c r="D69" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1936,7 +1973,7 @@
       <c r="D70" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1953,18 +1990,18 @@
       <c r="D71" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="14" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
     </row>
     <row r="73" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
@@ -1979,7 +2016,7 @@
       <c r="D73" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="E73" s="13" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1996,7 +2033,7 @@
       <c r="D74" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="14" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2013,7 +2050,7 @@
       <c r="D75" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="14" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2030,7 +2067,7 @@
       <c r="D76" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2047,7 +2084,7 @@
       <c r="D77" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2064,7 +2101,7 @@
       <c r="D78" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E78" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2081,7 +2118,7 @@
       <c r="D79" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E79" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2098,7 +2135,7 @@
       <c r="D80" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E80" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2115,7 +2152,7 @@
       <c r="D81" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E81" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2132,7 +2169,7 @@
       <c r="D82" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2149,7 +2186,7 @@
       <c r="D83" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="E83" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2166,7 +2203,7 @@
       <c r="D84" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2183,7 +2220,7 @@
       <c r="D85" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2200,7 +2237,7 @@
       <c r="D86" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2217,7 +2254,7 @@
       <c r="D87" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E87" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2234,7 +2271,7 @@
       <c r="D88" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2290,13 +2327,15 @@
     <row r="134" ht="24.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="135" ht="24.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A72:E72"/>
+    <mergeCell ref="F15:F16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDFE655-CC8B-43F0-92BB-3B3244FEB650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1C8352-D18B-473B-9344-28C681913AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="83">
   <si>
     <t>课程进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -347,6 +347,10 @@
   </si>
   <si>
     <t>中值定理中微分方程反解C法（P9）未看</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中值定理解题课2考法六、七等刷完等级1前面五个考法完全掌握再学习</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -494,9 +498,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -509,7 +510,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -792,28 +793,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="48.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29" style="17" customWidth="1"/>
+    <col min="6" max="6" width="29" style="5" customWidth="1"/>
     <col min="7" max="7" width="37.88671875" style="1" customWidth="1"/>
     <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -826,14 +827,14 @@
       <c r="D2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46146</v>
       </c>
@@ -846,11 +847,11 @@
       <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46147</v>
       </c>
@@ -863,11 +864,11 @@
       <c r="D4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46148</v>
       </c>
@@ -880,11 +881,11 @@
       <c r="D5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="14">
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46149</v>
       </c>
@@ -897,20 +898,20 @@
       <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-    </row>
-    <row r="8" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
@@ -923,11 +924,11 @@
       <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46150</v>
       </c>
@@ -937,14 +938,14 @@
       <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>2.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46151</v>
       </c>
@@ -954,14 +955,14 @@
       <c r="C10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46152</v>
       </c>
@@ -971,14 +972,14 @@
       <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46153</v>
       </c>
@@ -988,48 +989,48 @@
       <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46154</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46155</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46156</v>
       </c>
@@ -1042,30 +1043,34 @@
       <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="16" t="s">
+      <c r="E15" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46157</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="11" t="s">
         <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="16"/>
+      <c r="E16" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
@@ -1080,7 +1085,7 @@
       <c r="D17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1097,7 +1102,7 @@
       <c r="D18" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1114,7 +1119,7 @@
       <c r="D19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1131,7 +1136,7 @@
       <c r="D20" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1148,7 +1153,7 @@
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1165,7 +1170,7 @@
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1182,7 +1187,7 @@
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1199,7 +1204,7 @@
       <c r="D24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1216,7 +1221,7 @@
       <c r="D25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1233,7 +1238,7 @@
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1250,7 +1255,7 @@
       <c r="D27" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1267,7 +1272,7 @@
       <c r="D28" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1284,7 +1289,7 @@
       <c r="D29" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1301,7 +1306,7 @@
       <c r="D30" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1318,7 +1323,7 @@
       <c r="D31" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1335,7 +1340,7 @@
       <c r="D32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1352,7 +1357,7 @@
       <c r="D33" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1369,7 +1374,7 @@
       <c r="D34" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1386,7 +1391,7 @@
       <c r="D35" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1403,7 +1408,7 @@
       <c r="D36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1420,7 +1425,7 @@
       <c r="D37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1437,7 +1442,7 @@
       <c r="D38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1454,18 +1459,18 @@
       <c r="D39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
     </row>
     <row r="41" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
@@ -1480,7 +1485,7 @@
       <c r="D41" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1497,7 +1502,7 @@
       <c r="D42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1514,7 +1519,7 @@
       <c r="D43" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1531,7 +1536,7 @@
       <c r="D44" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1548,7 +1553,7 @@
       <c r="D45" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1565,7 +1570,7 @@
       <c r="D46" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1582,7 +1587,7 @@
       <c r="D47" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1599,7 +1604,7 @@
       <c r="D48" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1616,7 +1621,7 @@
       <c r="D49" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1633,7 +1638,7 @@
       <c r="D50" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1650,7 +1655,7 @@
       <c r="D51" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1667,7 +1672,7 @@
       <c r="D52" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1684,7 +1689,7 @@
       <c r="D53" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1701,7 +1706,7 @@
       <c r="D54" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1718,7 +1723,7 @@
       <c r="D55" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1735,7 +1740,7 @@
       <c r="D56" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E56" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1752,7 +1757,7 @@
       <c r="D57" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1769,7 +1774,7 @@
       <c r="D58" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1786,7 +1791,7 @@
       <c r="D59" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1803,7 +1808,7 @@
       <c r="D60" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1820,7 +1825,7 @@
       <c r="D61" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1837,7 +1842,7 @@
       <c r="D62" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1854,7 +1859,7 @@
       <c r="D63" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1871,7 +1876,7 @@
       <c r="D64" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E64" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1888,7 +1893,7 @@
       <c r="D65" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E65" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1905,7 +1910,7 @@
       <c r="D66" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1922,7 +1927,7 @@
       <c r="D67" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E67" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1939,7 +1944,7 @@
       <c r="D68" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1956,7 +1961,7 @@
       <c r="D69" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1973,7 +1978,7 @@
       <c r="D70" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1990,18 +1995,18 @@
       <c r="D71" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
     </row>
     <row r="73" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
@@ -2016,7 +2021,7 @@
       <c r="D73" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="13" t="s">
+      <c r="E73" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2033,7 +2038,7 @@
       <c r="D74" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E74" s="14" t="s">
+      <c r="E74" s="13" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2050,7 +2055,7 @@
       <c r="D75" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="13" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2067,7 +2072,7 @@
       <c r="D76" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E76" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2084,7 +2089,7 @@
       <c r="D77" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2101,7 +2106,7 @@
       <c r="D78" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2118,7 +2123,7 @@
       <c r="D79" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2135,7 +2140,7 @@
       <c r="D80" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2152,7 +2157,7 @@
       <c r="D81" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E81" s="14" t="s">
+      <c r="E81" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2169,7 +2174,7 @@
       <c r="D82" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E82" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2186,7 +2191,7 @@
       <c r="D83" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E83" s="14" t="s">
+      <c r="E83" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2203,7 +2208,7 @@
       <c r="D84" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="E84" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2220,7 +2225,7 @@
       <c r="D85" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="E85" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2237,7 +2242,7 @@
       <c r="D86" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E86" s="14" t="s">
+      <c r="E86" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2254,7 +2259,7 @@
       <c r="D87" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E87" s="14" t="s">
+      <c r="E87" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2271,7 +2276,7 @@
       <c r="D88" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="E88" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2327,7 +2332,8 @@
     <row r="134" ht="24.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="135" ht="24.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="G15:G16"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A40:E40"/>

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1C8352-D18B-473B-9344-28C681913AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B499803-1B66-4FAC-A2F9-43D2739038D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -969,7 +969,7 @@
       <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="11" t="s">
@@ -1079,7 +1079,7 @@
       <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="11" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -1096,7 +1096,7 @@
       <c r="B18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="2" t="s">

--- a/Diary/高数、线代、概统安排.xlsx
+++ b/Diary/高数、线代、概统安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B499803-1B66-4FAC-A2F9-43D2739038D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D11148-4B3E-4603-9888-1DD472A50558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9504" yWindow="2736" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="83">
   <si>
     <t>课程进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1147,7 +1147,7 @@
       <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -1164,7 +1164,7 @@
       <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="11" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -1181,7 +1181,7 @@
       <c r="B23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -1215,7 +1215,7 @@
       <c r="B25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -1252,7 +1252,7 @@
       <c r="C27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="9" t="s">
         <v>2</v>
       </c>
       <c r="E27" s="13" t="s">
@@ -1269,7 +1269,7 @@
       <c r="C28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="9" t="s">
         <v>2</v>
       </c>
       <c r="E28" s="13" t="s">
@@ -1286,7 +1286,7 @@
       <c r="C29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="9" t="s">
         <v>2</v>
       </c>
       <c r="E29" s="13" t="s">
@@ -1303,7 +1303,7 @@
       <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="9" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="13" t="s">
@@ -1320,7 +1320,7 @@
       <c r="C31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="9" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="13" t="s">
@@ -1334,10 +1334,10 @@
       <c r="B32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="C32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="13" t="s">
@@ -1453,7 +1453,7 @@
       <c r="B39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="5" t="s">
@@ -2032,9 +2032,7 @@
       <c r="B74" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C74" s="5"/>
       <c r="D74" s="5" t="s">
         <v>67</v>
       </c>
@@ -2049,9 +2047,7 @@
       <c r="B75" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C75" s="5"/>
       <c r="D75" s="5" t="s">
         <v>67</v>
       </c>
@@ -2066,9 +2062,7 @@
       <c r="B76" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C76" s="5"/>
       <c r="D76" s="5" t="s">
         <v>67</v>
       </c>
@@ -2083,9 +2077,7 @@
       <c r="B77" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C77" s="5"/>
       <c r="D77" s="5" t="s">
         <v>68</v>
       </c>
@@ -2100,9 +2092,7 @@
       <c r="B78" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C78" s="5"/>
       <c r="D78" s="5" t="s">
         <v>68</v>
       </c>
@@ -2117,9 +2107,7 @@
       <c r="B79" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C79" s="5"/>
       <c r="D79" s="5" t="s">
         <v>68</v>
       </c>
@@ -2134,9 +2122,7 @@
       <c r="B80" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C80" s="5"/>
       <c r="D80" s="5" t="s">
         <v>68</v>
       </c>
@@ -2151,9 +2137,7 @@
       <c r="B81" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C81" s="5"/>
       <c r="D81" s="5" t="s">
         <v>69</v>
       </c>
@@ -2168,9 +2152,7 @@
       <c r="B82" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C82" s="5"/>
       <c r="D82" s="5" t="s">
         <v>69</v>
       </c>
@@ -2185,9 +2167,7 @@
       <c r="B83" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C83" s="5"/>
       <c r="D83" s="5" t="s">
         <v>69</v>
       </c>
@@ -2202,9 +2182,7 @@
       <c r="B84" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C84" s="5"/>
       <c r="D84" s="5" t="s">
         <v>69</v>
       </c>
@@ -2219,9 +2197,7 @@
       <c r="B85" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C85" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C85" s="5"/>
       <c r="D85" s="5" t="s">
         <v>70</v>
       </c>
@@ -2236,9 +2212,7 @@
       <c r="B86" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C86" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C86" s="5"/>
       <c r="D86" s="5" t="s">
         <v>70</v>
       </c>
@@ -2253,9 +2227,7 @@
       <c r="B87" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C87" s="5"/>
       <c r="D87" s="5" t="s">
         <v>70</v>
       </c>
@@ -2270,9 +2242,7 @@
       <c r="B88" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C88" s="5"/>
       <c r="D88" s="5" t="s">
         <v>70</v>
       </c>
